--- a/01_プロジェクト/BUYMA購入者配布資料/BUYMA_海外買付管理表_購入者版.xlsx
+++ b/01_プロジェクト/BUYMA購入者配布資料/BUYMA_海外買付管理表_購入者版.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海外買付管理" sheetId="1" r:id="R788417392358462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" r:id="R6a9a790f063a4769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="経費・送金明細" sheetId="3" r:id="Raa876d818c534ca6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海外買付管理" sheetId="1" r:id="R54f5379d802347a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" r:id="R4d3e70845fc0448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="経費・送金明細" sheetId="3" r:id="R751b3d1306d94cb7"/>
   </x:sheets>
 </x:workbook>
 </file>
